--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-04.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-04.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T13"/>
+  <dimension ref="A1:Y13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,31 @@
           <t>PnL_R$</t>
         </is>
       </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Fonte_Placar</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>PnL_stake_u</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Convencao_PnL</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Placar_Original</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Resultado_Original</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -610,10 +635,33 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>0.95</v>
+        <v>0.14844</v>
       </c>
       <c r="T2" t="n">
         <v>14.84</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>b365:fuzzy0.94</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>LIABILITY=1u;comissao=5%</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>5x1</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -696,10 +744,33 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>0.95</v>
+        <v>0.18269</v>
       </c>
       <c r="T3" t="n">
         <v>18.27</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>b365:fuzzy0.91</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>LIABILITY=1u;comissao=5%</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2x0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -782,10 +853,33 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>0.95</v>
+        <v>0.20213</v>
       </c>
       <c r="T4" t="n">
-        <v>20.22</v>
+        <v>20.21</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>betfair:fuzzy0.95</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>LIABILITY=1u;comissao=5%</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4x1</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -868,10 +962,33 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>0.95</v>
+        <v>0.16964</v>
       </c>
       <c r="T5" t="n">
-        <v>16.97</v>
+        <v>16.96</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>betfair:exato</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>LIABILITY=1u;comissao=5%</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1x2</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -954,10 +1071,33 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>0.95</v>
+        <v>0.16964</v>
       </c>
       <c r="T6" t="n">
-        <v>16.97</v>
+        <v>16.96</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>betfair:fuzzy0.87</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>LIABILITY=1u;comissao=5%</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>5x0</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1040,10 +1180,33 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>0.95</v>
+        <v>0.15833</v>
       </c>
       <c r="T7" t="n">
-        <v>15.84</v>
+        <v>15.83</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>betfair:fuzzy0.92</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>LIABILITY=1u;comissao=5%</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0x2</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1126,10 +1289,33 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>0.95</v>
+        <v>0.15833</v>
       </c>
       <c r="T8" t="n">
-        <v>15.84</v>
+        <v>15.83</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>b365:fuzzy0.88</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>LIABILITY=1u;comissao=5%</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0x1</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1212,10 +1398,33 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>0.95</v>
+        <v>0.17593</v>
       </c>
       <c r="T9" t="n">
         <v>17.59</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>betfair:exato</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>LIABILITY=1u;comissao=5%</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0x2</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -1298,10 +1507,33 @@
         </is>
       </c>
       <c r="S10" t="n">
-        <v>-6.2</v>
+        <v>-1</v>
       </c>
       <c r="T10" t="n">
         <v>-100</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>betfair:exato</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>LIABILITY=1u;comissao=5%</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>1x0</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1364,30 +1596,37 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
           <t>1x2</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="S11" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T11" t="n">
-        <v>17.59</v>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -1470,10 +1709,33 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>0.95</v>
+        <v>0.11047</v>
       </c>
       <c r="T12" t="n">
         <v>11.05</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>betfair:fuzzy0.92</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>LIABILITY=1u;comissao=5%</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>2x1</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1556,10 +1818,33 @@
         </is>
       </c>
       <c r="S13" t="n">
-        <v>0.95</v>
+        <v>0.05</v>
       </c>
       <c r="T13" t="n">
         <v>5</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>betfair:exato</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>LIABILITY=1u;comissao=5%</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>2x0</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-04.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-04.xlsx
@@ -1596,15 +1596,17 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr"/>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
       <c r="Q11" t="n">
         <v>0.95</v>
       </c>
@@ -1613,11 +1615,25 @@
           <t>GREEN</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
+      <c r="S11" t="n">
+        <v>0.17593</v>
+      </c>
+      <c r="T11" t="n">
+        <v>17.59</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>LIABILITY=1u;comissao=5%</t>
+        </is>
+      </c>
       <c r="X11" t="inlineStr">
         <is>
           <t>1x2</t>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-04.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-04.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y13"/>
+  <dimension ref="A1:T13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,31 +529,6 @@
           <t>PnL_R$</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Fonte_Placar</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>PnL_stake_u</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Convencao_PnL</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Placar_Original</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Resultado_Original</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -635,33 +610,10 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>0.14844</v>
+        <v>0.95</v>
       </c>
       <c r="T2" t="n">
         <v>14.84</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>b365:fuzzy0.94</t>
-        </is>
-      </c>
-      <c r="V2" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>LIABILITY=1u;comissao=5%</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>5x1</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
       </c>
     </row>
     <row r="3">
@@ -744,33 +696,10 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>0.18269</v>
+        <v>0.95</v>
       </c>
       <c r="T3" t="n">
         <v>18.27</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>b365:fuzzy0.91</t>
-        </is>
-      </c>
-      <c r="V3" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>LIABILITY=1u;comissao=5%</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>2x0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
       </c>
     </row>
     <row r="4">
@@ -853,33 +782,10 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>0.20213</v>
+        <v>0.95</v>
       </c>
       <c r="T4" t="n">
-        <v>20.21</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>betfair:fuzzy0.95</t>
-        </is>
-      </c>
-      <c r="V4" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>LIABILITY=1u;comissao=5%</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>4x1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
+        <v>20.22</v>
       </c>
     </row>
     <row r="5">
@@ -962,33 +868,10 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>0.16964</v>
+        <v>0.95</v>
       </c>
       <c r="T5" t="n">
-        <v>16.96</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>betfair:exato</t>
-        </is>
-      </c>
-      <c r="V5" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>LIABILITY=1u;comissao=5%</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1x2</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
+        <v>16.97</v>
       </c>
     </row>
     <row r="6">
@@ -1071,33 +954,10 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>0.16964</v>
+        <v>0.95</v>
       </c>
       <c r="T6" t="n">
-        <v>16.96</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>betfair:fuzzy0.87</t>
-        </is>
-      </c>
-      <c r="V6" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>LIABILITY=1u;comissao=5%</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>5x0</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
+        <v>16.97</v>
       </c>
     </row>
     <row r="7">
@@ -1180,33 +1040,10 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>0.15833</v>
+        <v>0.95</v>
       </c>
       <c r="T7" t="n">
-        <v>15.83</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>betfair:fuzzy0.92</t>
-        </is>
-      </c>
-      <c r="V7" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>LIABILITY=1u;comissao=5%</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>0x2</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
+        <v>15.84</v>
       </c>
     </row>
     <row r="8">
@@ -1289,33 +1126,10 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>0.15833</v>
+        <v>0.95</v>
       </c>
       <c r="T8" t="n">
-        <v>15.83</v>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>b365:fuzzy0.88</t>
-        </is>
-      </c>
-      <c r="V8" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>LIABILITY=1u;comissao=5%</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0x1</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
+        <v>15.84</v>
       </c>
     </row>
     <row r="9">
@@ -1398,33 +1212,10 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>0.17593</v>
+        <v>0.95</v>
       </c>
       <c r="T9" t="n">
         <v>17.59</v>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>betfair:exato</t>
-        </is>
-      </c>
-      <c r="V9" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>LIABILITY=1u;comissao=5%</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>0x2</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
       </c>
     </row>
     <row r="10">
@@ -1507,33 +1298,10 @@
         </is>
       </c>
       <c r="S10" t="n">
-        <v>-1</v>
+        <v>-6.2</v>
       </c>
       <c r="T10" t="n">
         <v>-100</v>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>betfair:exato</t>
-        </is>
-      </c>
-      <c r="V10" t="n">
-        <v>-6.2</v>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>LIABILITY=1u;comissao=5%</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>1x0</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>RED</t>
-        </is>
       </c>
     </row>
     <row r="11">
@@ -1616,33 +1384,10 @@
         </is>
       </c>
       <c r="S11" t="n">
-        <v>0.17593</v>
+        <v>0.95</v>
       </c>
       <c r="T11" t="n">
         <v>17.59</v>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="V11" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>LIABILITY=1u;comissao=5%</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>1x2</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
       </c>
     </row>
     <row r="12">
@@ -1725,33 +1470,10 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>0.11047</v>
+        <v>0.95</v>
       </c>
       <c r="T12" t="n">
         <v>11.05</v>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>betfair:fuzzy0.92</t>
-        </is>
-      </c>
-      <c r="V12" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>LIABILITY=1u;comissao=5%</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>2x1</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
       </c>
     </row>
     <row r="13">
@@ -1834,33 +1556,10 @@
         </is>
       </c>
       <c r="S13" t="n">
-        <v>0.05</v>
+        <v>0.95</v>
       </c>
       <c r="T13" t="n">
         <v>5</v>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>betfair:exato</t>
-        </is>
-      </c>
-      <c r="V13" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>LIABILITY=1u;comissao=5%</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>2x0</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
       </c>
     </row>
   </sheetData>
